--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-04-2026.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£32.08</t>
+          <t>£19.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£54.92</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£47.28</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£55.96</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out.</t>
+          <t>£1424.57</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>£1387.2</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
